--- a/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>RPTX</t>
   </si>
@@ -656,152 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>112500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6900</v>
-      </c>
-      <c r="L8" s="3">
-        <v>300</v>
       </c>
       <c r="M8" s="3">
         <v>300</v>
       </c>
       <c r="N8" s="3">
+        <v>300</v>
+      </c>
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -817,8 +820,8 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -826,8 +829,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -894,8 +900,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1000,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E12" s="3">
         <v>32700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>31500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3700</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1140,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1162,18 +1181,18 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>1300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1186,14 +1205,17 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1245,8 +1267,8 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,118 +1308,122 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E17" s="3">
         <v>40600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>37800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>35200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4800</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-38400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-34700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>73400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-38700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-34800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,8 +1448,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,50 +1477,51 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E20" s="3">
         <v>3200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1513,50 +1546,53 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-34700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-30900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>76000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-37500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-28300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-31200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-21200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1617,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,117 +1688,123 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-31300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>75500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-34700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4700</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-16300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1600</v>
-      </c>
-      <c r="P24" s="3">
-        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
@@ -1768,25 +1813,28 @@
         <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>75500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-11800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4800</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>75500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-11800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4800</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,50 +2327,53 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,76 +2398,82 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>75500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4800</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>75500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4800</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,59 +2743,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>111300</v>
+      </c>
+      <c r="E41" s="3">
         <v>107400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>115500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>121500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>159500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>155200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>275800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>305100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>334400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>261000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>293600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>311400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>326200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>347900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>369900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>83700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,43 +2812,46 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E42" s="3">
         <v>142700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>165100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>192700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>184400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>215200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7400</v>
-      </c>
-      <c r="L42" s="3">
-        <v>7200</v>
       </c>
       <c r="M42" s="3">
         <v>7200</v>
       </c>
       <c r="N42" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2794,59 +2883,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E43" s="3">
         <v>19500</v>
-      </c>
-      <c r="E43" s="3">
-        <v>7000</v>
       </c>
       <c r="F43" s="3">
         <v>7000</v>
       </c>
       <c r="G43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H43" s="3">
         <v>4300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3400</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2862,8 +2954,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,59 +3025,62 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E45" s="3">
         <v>5600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,59 +3096,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>243700</v>
+      </c>
+      <c r="E46" s="3">
         <v>275100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>291900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>325500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>354000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>390600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>289700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>319200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>351400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>280400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>309200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>328200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>346600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>361300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>377300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>87900</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3066,16 +3167,19 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>2300</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
+      <c r="E47" s="3">
+        <v>2300</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -3092,8 +3196,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3134,59 +3238,62 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E48" s="3">
         <v>8600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3100</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,8 +3309,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3270,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3522,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3421,44 +3540,44 @@
         <v>400</v>
       </c>
       <c r="G52" s="3">
+        <v>400</v>
+      </c>
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2600</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,59 +3664,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E54" s="3">
         <v>286400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>301600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>336300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>364100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>409200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>308000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>337100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>368700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>295600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>320700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>339100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>357100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>370200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>381700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>93600</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,59 +3791,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
         <v>5400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,8 +3860,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3798,59 +3931,62 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E59" s="3">
         <v>43500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>77300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>78200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>32500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>32800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,59 +4002,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E60" s="3">
         <v>49000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>80900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>78600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>39400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>23200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7300</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,8 +4073,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4002,59 +4144,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>41500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>43100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>45200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>52300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>59000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>59200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>59300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>58300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8400</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,59 +4428,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E66" s="3">
         <v>53000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>56200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>85100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>84600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>103400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>82500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>80300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>71400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>70300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>69400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>68100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15700</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4552,11 +4719,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>136000</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,59 +4810,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-333100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-305100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-286200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-274300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-239300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-207700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-283100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-245000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-210300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-182000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-151100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-124800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-103400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-88100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-74300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-62500</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,59 +5094,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>212100</v>
+      </c>
+      <c r="E76" s="3">
         <v>233400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>245400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>251200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>279500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>305800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>225500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>258700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>288400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>218300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>245100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>267700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>286800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>300800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>313700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-58100</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>75500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4800</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5412,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5227,10 +5425,10 @@
         <v>500</v>
       </c>
       <c r="F83" s="3">
+        <v>500</v>
+      </c>
+      <c r="G83" s="3">
         <v>400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>500</v>
       </c>
       <c r="H83" s="3">
         <v>500</v>
@@ -5242,7 +5440,7 @@
         <v>500</v>
       </c>
       <c r="K83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -5251,13 +5449,13 @@
         <v>400</v>
       </c>
       <c r="N83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -5269,13 +5467,13 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>100</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5283,8 +5481,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-34300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-31800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-29600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>88200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-20700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-32800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-18100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>36700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5936,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E94" s="3">
         <v>24500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>28400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>34100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-208900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>400</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-400</v>
       </c>
       <c r="L94" s="3">
         <v>-400</v>
       </c>
       <c r="M94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,135 +6529,141 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>200</v>
       </c>
       <c r="J100" s="3">
         <v>200</v>
       </c>
       <c r="K100" s="3">
+        <v>200</v>
+      </c>
+      <c r="L100" s="3">
         <v>94600</v>
-      </c>
-      <c r="L100" s="3">
-        <v>400</v>
       </c>
       <c r="M100" s="3">
         <v>400</v>
       </c>
       <c r="N100" s="3">
+        <v>400</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>249000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>21000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
       <c r="O101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3">
         <v>200</v>
       </c>
       <c r="Q101" s="3">
+        <v>200</v>
+      </c>
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
@@ -6423,72 +6671,78 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-38100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-120600</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-29300</v>
       </c>
       <c r="J102" s="3">
         <v>-29300</v>
       </c>
       <c r="K102" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="L102" s="3">
         <v>73400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-32900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-21700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>286200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23700</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
   <si>
     <t>RPTX</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E8" s="3">
         <v>13000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>112500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6900</v>
-      </c>
-      <c r="M8" s="3">
-        <v>300</v>
       </c>
       <c r="N8" s="3">
         <v>300</v>
       </c>
       <c r="O8" s="3">
+        <v>300</v>
+      </c>
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,8 +827,8 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -832,8 +836,11 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -903,8 +910,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E12" s="3">
         <v>35300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>32700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>31200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3700</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,31 +1160,34 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1184,18 +1204,18 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1208,14 +1228,17 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1270,8 +1293,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,124 +1335,128 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E17" s="3">
         <v>43900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>37800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>39400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4800</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-38400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-34700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>73400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-38700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-34800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-31700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-26600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1451,8 +1481,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,53 +1511,54 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1549,53 +1583,56 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-27300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-34700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>76000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-37500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-34200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-31200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-26300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-21200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,8 +1657,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1691,123 +1731,129 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-31300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>75500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-38100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4700</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-16300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1600</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
@@ -1816,25 +1862,28 @@
         <v>100</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>75500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4800</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>75500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,53 +2397,56 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2401,79 +2471,85 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>75500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-12600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>75500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-12600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,62 +2830,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E41" s="3">
         <v>111300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>107400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>115500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>121500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>159500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>155200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>275800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>305100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>334400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>261000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>293600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>311400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>326200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>347900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>369900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>83700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,46 +2902,49 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>133800</v>
+      </c>
+      <c r="E42" s="3">
         <v>112400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>142700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>165100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>192700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>184400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>215200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7400</v>
-      </c>
-      <c r="M42" s="3">
-        <v>7200</v>
       </c>
       <c r="N42" s="3">
         <v>7200</v>
       </c>
       <c r="O42" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2886,62 +2976,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E43" s="3">
         <v>15300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19500</v>
-      </c>
-      <c r="F43" s="3">
-        <v>7000</v>
       </c>
       <c r="G43" s="3">
         <v>7000</v>
       </c>
       <c r="H43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I43" s="3">
         <v>4300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,8 +3050,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3028,62 +3124,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E45" s="3">
         <v>4700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3099,62 +3198,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>254700</v>
+      </c>
+      <c r="E46" s="3">
         <v>243700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>275100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>291900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>325500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>354000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>390600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>289700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>319200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>351400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>280400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>309200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>328200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>346600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>361300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>377300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>87900</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,19 +3272,22 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="E47" s="3">
         <v>2300</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+      <c r="F47" s="3">
+        <v>2300</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -3199,8 +3304,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3241,62 +3346,65 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E48" s="3">
         <v>7500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3312,8 +3420,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3383,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,13 +3642,16 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
@@ -3543,44 +3663,44 @@
         <v>400</v>
       </c>
       <c r="H52" s="3">
+        <v>400</v>
+      </c>
+      <c r="I52" s="3">
         <v>500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2600</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,62 +3790,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>263100</v>
+      </c>
+      <c r="E54" s="3">
         <v>253900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>286400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>301600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>336300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>364100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>409200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>308000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>337100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>368700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>295600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>320700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>339100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>357100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>370200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>381700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>93600</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,62 +3922,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,8 +3994,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3934,62 +4068,65 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E59" s="3">
         <v>36700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>77300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>78200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>52500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>32500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>32800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,62 +4142,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E60" s="3">
         <v>39100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>80900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>78600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>39400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>23400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7300</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,8 +4216,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4147,62 +4290,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>41500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>43100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>44400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>45200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>54000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>59000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>59200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>59300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>58300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8400</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,62 +4586,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E66" s="3">
         <v>41800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>56200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>84600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>103400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>78500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>80300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>75600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>71400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>70300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>69400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>68100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15700</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4722,11 +4890,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>136000</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,62 +4984,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-319900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-333100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-305100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-286200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-274300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-239300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-207700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-283100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-245000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-210300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-182000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-151100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-124800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-103400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-88100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-74300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-62500</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,62 +5280,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>232000</v>
+      </c>
+      <c r="E76" s="3">
         <v>212100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>233400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>245400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>251200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>279500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>305800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>225500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>258700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>288400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>218300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>245100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>267700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>286800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>300800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>313700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-58100</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>75500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-12600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,8 +5611,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5428,10 +5627,10 @@
         <v>500</v>
       </c>
       <c r="G83" s="3">
+        <v>500</v>
+      </c>
+      <c r="H83" s="3">
         <v>400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
@@ -5443,7 +5642,7 @@
         <v>500</v>
       </c>
       <c r="L83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M83" s="3">
         <v>400</v>
@@ -5452,13 +5651,13 @@
         <v>400</v>
       </c>
       <c r="O83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -5470,13 +5669,13 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>100</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5484,8 +5683,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-34300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-31800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-29600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>88200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-20700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-32800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-18100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-20100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>36700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E94" s="3">
         <v>31900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>28400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>34100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-208900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>400</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-400</v>
       </c>
       <c r="M94" s="3">
         <v>-400</v>
       </c>
       <c r="N94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,141 +6775,147 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
-      </c>
-      <c r="J100" s="3">
-        <v>200</v>
       </c>
       <c r="K100" s="3">
         <v>200</v>
       </c>
       <c r="L100" s="3">
+        <v>200</v>
+      </c>
+      <c r="M100" s="3">
         <v>94600</v>
-      </c>
-      <c r="M100" s="3">
-        <v>400</v>
       </c>
       <c r="N100" s="3">
         <v>400</v>
       </c>
       <c r="O100" s="3">
+        <v>400</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>249000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>21000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
       <c r="P101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="3">
         <v>200</v>
       </c>
       <c r="R101" s="3">
+        <v>200</v>
+      </c>
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -6674,75 +6923,81 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E102" s="3">
         <v>3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-38100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-120600</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-29300</v>
       </c>
       <c r="K102" s="3">
         <v>-29300</v>
       </c>
       <c r="L102" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="M102" s="3">
         <v>73400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-32900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-22100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>286200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>23700</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>RPTX</t>
   </si>
@@ -656,165 +656,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E8" s="3">
         <v>52400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>112500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6900</v>
-      </c>
-      <c r="N8" s="3">
-        <v>300</v>
       </c>
       <c r="O8" s="3">
         <v>300</v>
       </c>
       <c r="P8" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -830,8 +834,8 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -839,8 +843,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -913,8 +920,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E12" s="3">
         <v>33000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>35300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>32700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>33800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3700</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1189,8 +1209,8 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
@@ -1207,18 +1227,18 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>1300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,14 +1251,17 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1296,8 +1319,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,130 +1362,134 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E17" s="3">
         <v>41600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>37800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>39100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4800</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="E18" s="3">
         <v>10800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-30900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-38400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-34700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>73400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-38700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-34800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-31700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-26600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1484,8 +1514,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,56 +1545,57 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1586,56 +1620,59 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E21" s="3">
         <v>14300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-27300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-34700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-30900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>76000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-37500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-34200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-28300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-26300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,8 +1697,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,129 +1774,135 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E23" s="3">
         <v>13800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>75500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4700</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-16300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1600</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
@@ -1865,25 +1911,28 @@
         <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E26" s="3">
         <v>13200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>75500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-38100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4800</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E27" s="3">
         <v>13200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>75500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-30900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4800</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,56 +2467,59 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2474,82 +2544,88 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E33" s="3">
         <v>13200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>75500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-38100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-30900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-12600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4800</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E35" s="3">
         <v>13200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>75500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-38100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-30900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-12600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4800</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,65 +2917,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E41" s="3">
         <v>103200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>111300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>107400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>115500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>121500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>159500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>155200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>275800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>305100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>334400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>261000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>293600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>311400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>326200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>347900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>369900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>83700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2905,49 +2992,52 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>128300</v>
+      </c>
+      <c r="E42" s="3">
         <v>133800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>112400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>142700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>165100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>192700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>184400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>215200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7400</v>
-      </c>
-      <c r="N42" s="3">
-        <v>7200</v>
       </c>
       <c r="O42" s="3">
         <v>7200</v>
       </c>
       <c r="P42" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2979,65 +3069,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E43" s="3">
         <v>14200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19500</v>
-      </c>
-      <c r="G43" s="3">
-        <v>7000</v>
       </c>
       <c r="H43" s="3">
         <v>7000</v>
       </c>
       <c r="I43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J43" s="3">
         <v>4300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,65 +3223,68 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,65 +3300,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>228500</v>
+      </c>
+      <c r="E46" s="3">
         <v>254700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>243700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>275100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>291900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>325500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>354000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>390600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>289700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>319200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>351400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>280400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>309200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>328200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>346600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>361300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>377300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>87900</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,22 +3377,25 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E47" s="3">
         <v>1600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2300</v>
       </c>
       <c r="F47" s="3">
         <v>2300</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+      <c r="G47" s="3">
+        <v>2300</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -3307,8 +3412,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3349,65 +3454,68 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E48" s="3">
         <v>6500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3100</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,8 +3531,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3654,7 +3774,7 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
@@ -3666,44 +3786,44 @@
         <v>400</v>
       </c>
       <c r="I52" s="3">
+        <v>400</v>
+      </c>
+      <c r="J52" s="3">
         <v>500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,65 +3916,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>235300</v>
+      </c>
+      <c r="E54" s="3">
         <v>263100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>253900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>286400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>301600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>336300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>364100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>409200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>308000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>337100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>368700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>295600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>320700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>339100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>357100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>370200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>381700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>93600</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,65 +4053,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E57" s="3">
         <v>6800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4128,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4071,65 +4205,68 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E59" s="3">
         <v>23700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>43500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>48400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>77300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>78200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>32500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>32800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4145,65 +4282,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E60" s="3">
         <v>30600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>49000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>80900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>78600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>61900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7300</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4359,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4293,65 +4436,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>41500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>43100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>44400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>45200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>54000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>52300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>59000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>59200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>59300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>58300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,65 +4744,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E66" s="3">
         <v>31100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>56200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>84600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>103400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>80300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>75600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>71400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>70300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>69400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>68100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15700</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4893,11 +5061,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>136000</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,65 +5158,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-354700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-319900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-333100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-305100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-286200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-274300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-239300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-207700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-283100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-245000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-210300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-182000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-151100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-124800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-103400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-88100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-74300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-62500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,65 +5466,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E76" s="3">
         <v>232000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>212100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>233400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>245400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>251200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>279500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>305800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>225500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>258700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>288400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>218300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>245100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>267700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>286800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>300800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>313700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-58100</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E81" s="3">
         <v>13200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>75500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-38100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-30900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-12600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4800</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5630,10 +5829,10 @@
         <v>500</v>
       </c>
       <c r="H83" s="3">
+        <v>500</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
@@ -5645,7 +5844,7 @@
         <v>500</v>
       </c>
       <c r="M83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
@@ -5654,13 +5853,13 @@
         <v>400</v>
       </c>
       <c r="P83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q83" s="3">
         <v>300</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -5672,13 +5871,13 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>100</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="E89" s="3">
         <v>11900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-28200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-32900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-34300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-31800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-29600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>88200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-32800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-20100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>36700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6167,73 +6388,76 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>31900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>28400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>34100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-208900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>400</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-400</v>
       </c>
       <c r="N94" s="3">
         <v>-400</v>
       </c>
       <c r="O94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,82 +7021,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>200</v>
       </c>
       <c r="L100" s="3">
         <v>200</v>
       </c>
       <c r="M100" s="3">
+        <v>200</v>
+      </c>
+      <c r="N100" s="3">
         <v>94600</v>
-      </c>
-      <c r="N100" s="3">
-        <v>400</v>
       </c>
       <c r="O100" s="3">
         <v>400</v>
       </c>
       <c r="P100" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>249000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>21000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6861,64 +7110,64 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R101" s="3">
         <v>200</v>
       </c>
       <c r="S101" s="3">
+        <v>200</v>
+      </c>
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>500</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
@@ -6926,78 +7175,84 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-38100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-120600</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-29300</v>
       </c>
       <c r="L102" s="3">
         <v>-29300</v>
       </c>
       <c r="M102" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="N102" s="3">
         <v>73400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-32900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-22100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>286200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23700</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>RPTX</t>
   </si>
@@ -656,172 +656,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>1100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>52400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>112500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6900</v>
-      </c>
-      <c r="O8" s="3">
-        <v>300</v>
       </c>
       <c r="P8" s="3">
         <v>300</v>
       </c>
       <c r="Q8" s="3">
+        <v>300</v>
+      </c>
+      <c r="R8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -837,8 +841,8 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -846,31 +850,34 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>30100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>33000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>32900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>32700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>33800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>31800</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -923,31 +930,34 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>19400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-26200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>30100</v>
+        <v>28600</v>
       </c>
       <c r="E12" s="3">
+        <v>30300</v>
+      </c>
+      <c r="F12" s="3">
+        <v>33300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>35700</v>
+      </c>
+      <c r="H12" s="3">
         <v>33000</v>
       </c>
-      <c r="F12" s="3">
-        <v>35300</v>
-      </c>
-      <c r="G12" s="3">
-        <v>32700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>33800</v>
-      </c>
       <c r="I12" s="3">
-        <v>31800</v>
+        <v>34200</v>
       </c>
       <c r="J12" s="3">
+        <v>32200</v>
+      </c>
+      <c r="K12" s="3">
         <v>29900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>31500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3700</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,37 +1200,40 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1230,18 +1250,18 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,37 +1274,40 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1322,8 +1345,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,136 +1389,140 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E17" s="3">
         <v>38400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>41600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4800</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-37300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-30900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-38400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-34700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>73400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-38700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-34800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-28700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-31700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1517,8 +1547,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,59 +1579,60 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1623,59 +1657,62 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-34000</v>
+        <v>-34400</v>
       </c>
       <c r="E21" s="3">
-        <v>14300</v>
+        <v>-36900</v>
       </c>
       <c r="F21" s="3">
-        <v>-27300</v>
+        <v>11300</v>
       </c>
       <c r="G21" s="3">
-        <v>-34700</v>
+        <v>-30400</v>
       </c>
       <c r="H21" s="3">
-        <v>-8300</v>
+        <v>-38000</v>
       </c>
       <c r="I21" s="3">
-        <v>-30900</v>
+        <v>-11800</v>
       </c>
       <c r="J21" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-16200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>76000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-37500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-34200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-28300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-31200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-21200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,31 +1737,34 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1777,135 +1817,141 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>75500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-34700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-16300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1600</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
@@ -1914,25 +1960,28 @@
         <v>100</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>75500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-15300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>75500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-30900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-15300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,59 +2537,62 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2800</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,85 +2617,91 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>75500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-30900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-15300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-13800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>75500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-30900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-15300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-13800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,68 +3004,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E41" s="3">
         <v>79800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>103200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>111300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>107400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>115500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>121500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>159500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>155200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>275800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>305100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>334400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>261000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>293600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>311400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>326200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>347900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>369900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>83700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,52 +3082,55 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>98900</v>
+      </c>
+      <c r="E42" s="3">
         <v>128300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>133800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>112400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>142700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>165100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>192700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>184400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>215200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7400</v>
-      </c>
-      <c r="O42" s="3">
-        <v>7200</v>
       </c>
       <c r="P42" s="3">
         <v>7200</v>
       </c>
       <c r="Q42" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3072,68 +3162,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E43" s="3">
         <v>14600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19500</v>
-      </c>
-      <c r="H43" s="3">
-        <v>7000</v>
       </c>
       <c r="I43" s="3">
         <v>7000</v>
       </c>
       <c r="J43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K43" s="3">
         <v>4300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3400</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3149,31 +3242,34 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3226,68 +3322,71 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>5800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="L45" s="3">
         <v>5600</v>
       </c>
-      <c r="H45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>5700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>5600</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,68 +3402,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E46" s="3">
         <v>228500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>254700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>243700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>275100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>291900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>325500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>354000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>390600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>289700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>319200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>351400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>280400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>309200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>328200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>346600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>361300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>377300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>87900</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,22 +3482,25 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2300</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -3415,8 +3520,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3457,68 +3562,71 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3642,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,68 +3882,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>1400</v>
       </c>
       <c r="F52" s="3">
-        <v>400</v>
+        <v>1900</v>
       </c>
       <c r="G52" s="3">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="H52" s="3">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
       </c>
       <c r="J52" s="3">
+        <v>400</v>
+      </c>
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2600</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,68 +4042,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>206400</v>
+      </c>
+      <c r="E54" s="3">
         <v>235300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>263100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>253900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>286400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>301600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>336300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>364100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>409200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>308000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>337100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>368700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>295600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>320700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>339100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>357100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>370200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>381700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>93600</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,68 +4184,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E57" s="3">
         <v>7200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4131,31 +4262,34 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4208,68 +4342,71 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>24300</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>23700</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
-        <v>36700</v>
+        <v>1700</v>
       </c>
       <c r="G59" s="3">
-        <v>43500</v>
+        <v>10400</v>
       </c>
       <c r="H59" s="3">
-        <v>48400</v>
+        <v>20600</v>
       </c>
       <c r="I59" s="3">
-        <v>77300</v>
+        <v>24700</v>
       </c>
       <c r="J59" s="3">
+        <v>57800</v>
+      </c>
+      <c r="K59" s="3">
         <v>78200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>32500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4285,68 +4422,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E60" s="3">
         <v>31400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>39100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>49000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>80900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>78600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>61900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>39400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>23200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7300</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,31 +4502,34 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4439,68 +4582,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>5900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>41500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>43100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>44400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>45200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>54000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>52300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>59000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>59200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>59300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>58300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8400</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,68 +4902,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E66" s="3">
         <v>31700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>56200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>85100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>84600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>78500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>80300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>77400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>75600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>71400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>70300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>69400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>68100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15700</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5064,11 +5232,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>136000</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,68 +5332,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-389100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-354700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-319900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-333100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-305100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-286200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-274300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-239300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-207700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-283100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-245000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-210300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-182000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-151100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-124800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-103400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-88100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-74300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-62500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,68 +5652,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E76" s="3">
         <v>203700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>232000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>212100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>233400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>245400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>251200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>279500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>305800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>225500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>258700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>288400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>218300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>245100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>267700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>286800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>300800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>313700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-58100</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>75500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-30900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-15300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-13800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5823,7 +6022,7 @@
         <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G83" s="3">
         <v>500</v>
@@ -5832,7 +6031,7 @@
         <v>500</v>
       </c>
       <c r="I83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
@@ -5847,7 +6046,7 @@
         <v>500</v>
       </c>
       <c r="N83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
@@ -5856,13 +6055,13 @@
         <v>400</v>
       </c>
       <c r="Q83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
@@ -5874,13 +6073,13 @@
         <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>100</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,8 +6487,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6282,76 +6499,79 @@
         <v>-30500</v>
       </c>
       <c r="E89" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="F89" s="3">
         <v>11900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-34300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-31800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-29600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>88200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-20700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-32800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-14200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-20100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>36700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E94" s="3">
         <v>7100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>31900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>24500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>28400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>34100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-208900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>400</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-400</v>
       </c>
       <c r="O94" s="3">
         <v>-400</v>
       </c>
       <c r="P94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,31 +6949,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,153 +7267,159 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>200</v>
       </c>
       <c r="M100" s="3">
         <v>200</v>
       </c>
       <c r="N100" s="3">
+        <v>200</v>
+      </c>
+      <c r="O100" s="3">
         <v>94600</v>
-      </c>
-      <c r="O100" s="3">
-        <v>400</v>
       </c>
       <c r="P100" s="3">
         <v>400</v>
       </c>
       <c r="Q100" s="3">
+        <v>400</v>
+      </c>
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>249000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>21000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="K101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>100</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S101" s="3">
         <v>200</v>
       </c>
       <c r="T101" s="3">
+        <v>200</v>
+      </c>
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
@@ -7178,81 +7427,87 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-120600</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-29300</v>
       </c>
       <c r="M102" s="3">
         <v>-29300</v>
       </c>
       <c r="N102" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="O102" s="3">
         <v>73400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-32900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-21700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-22100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>286200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>23700</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>RPTX</t>
   </si>
@@ -656,179 +656,182 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>1100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>52400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>112500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6900</v>
-      </c>
-      <c r="P8" s="3">
-        <v>300</v>
       </c>
       <c r="Q8" s="3">
         <v>300</v>
       </c>
       <c r="R8" s="3">
+        <v>300</v>
+      </c>
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,8 +847,8 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -853,35 +856,38 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>-78100</v>
+      </c>
+      <c r="E9" s="3">
         <v>28400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33000</v>
       </c>
-      <c r="G9" s="3">
-        <v>32900</v>
-      </c>
       <c r="H9" s="3">
+        <v>-85100</v>
+      </c>
+      <c r="I9" s="3">
         <v>32700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>33800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31800</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,35 +939,38 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-28400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-29000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19400</v>
       </c>
-      <c r="G10" s="3">
-        <v>-19800</v>
-      </c>
       <c r="H10" s="3">
+        <v>98100</v>
+      </c>
+      <c r="I10" s="3">
         <v>-30600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-3500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-26200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1013,8 +1022,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,88 +1055,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E12" s="3">
         <v>28600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33300</v>
       </c>
-      <c r="G12" s="3">
-        <v>35700</v>
-      </c>
       <c r="H12" s="3">
+        <v>118000</v>
+      </c>
+      <c r="I12" s="3">
         <v>33000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>31200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3700</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,17 +1219,20 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1229,14 +1248,14 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1253,18 +1272,18 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>1300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1277,14 +1296,17 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1307,11 +1329,11 @@
         <v>500</v>
       </c>
       <c r="J15" s="3">
+        <v>500</v>
+      </c>
+      <c r="K15" s="3">
         <v>400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1348,8 +1370,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
@@ -1363,8 +1385,11 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,142 +1415,146 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E17" s="3">
         <v>34800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>41600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>43900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>35600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4800</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-34800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-37300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-38400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-34700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>73400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-38700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-34800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-26600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-17100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1550,8 +1579,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,22 +1612,23 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
@@ -1607,35 +1640,35 @@
         <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,62 +1693,65 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-34400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-36900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-38000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-16200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>76000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-37500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-34200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-28300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-31200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-21200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-16500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1740,8 +1776,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1766,8 +1805,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1820,141 +1859,147 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-33900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>75500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-38100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-34700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-16300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1600</v>
-      </c>
-      <c r="T24" s="3">
-        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
@@ -1963,25 +2008,28 @@
         <v>100</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>75500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-38100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-15300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>75500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-38100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-34800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-15300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-13800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,22 +2606,25 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
@@ -2567,35 +2636,35 @@
         <v>-100</v>
       </c>
       <c r="K32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2620,88 +2689,94 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>75500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-38100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-15300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-13800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>75500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-38100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-15300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-13800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,71 +3090,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E41" s="3">
         <v>80500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>79800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>103200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>111300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>107400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>115500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>121500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>159500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>155200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>275800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>305100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>334400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>261000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>293600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>311400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>326200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>347900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>369900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>83700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3085,55 +3171,58 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E42" s="3">
         <v>98900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>128300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>133800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>112400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>142700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>165100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>192700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>184400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>215200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7400</v>
-      </c>
-      <c r="P42" s="3">
-        <v>7200</v>
       </c>
       <c r="Q42" s="3">
         <v>7200</v>
       </c>
       <c r="R42" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3165,71 +3254,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E43" s="3">
         <v>14200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>7000</v>
       </c>
       <c r="J43" s="3">
         <v>7000</v>
       </c>
       <c r="K43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="L43" s="3">
         <v>4300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3245,8 +3337,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3271,8 +3366,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3325,8 +3420,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3351,45 +3449,45 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>5700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3405,71 +3503,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>171100</v>
+      </c>
+      <c r="E46" s="3">
         <v>200400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>228500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>254700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>243700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>275100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>291900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>325500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>354000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>390600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>289700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>319200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>351400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>280400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>309200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>328200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>346600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>361300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>377300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>87900</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,8 +3586,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3523,8 +3627,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3565,71 +3669,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3752,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3725,8 +3835,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,71 +4001,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2700</v>
       </c>
       <c r="H52" s="3">
         <v>2700</v>
       </c>
       <c r="I52" s="3">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="J52" s="3">
         <v>400</v>
       </c>
       <c r="K52" s="3">
+        <v>400</v>
+      </c>
+      <c r="L52" s="3">
         <v>500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3965,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,71 +4167,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>176500</v>
+      </c>
+      <c r="E54" s="3">
         <v>206400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>235300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>263100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>253900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>286400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>301600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>336300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>364100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>409200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>308000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>337100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>368700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>295600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>320700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>339100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>357100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>370200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>381700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>93600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,71 +4314,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
         <v>10700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4265,25 +4395,28 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E58" s="3">
         <v>2200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2300</v>
       </c>
       <c r="I58" s="3">
         <v>2300</v>
@@ -4292,7 +4425,7 @@
         <v>2300</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4345,71 +4478,74 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>57800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>78200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>52500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>34400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,71 +4561,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E60" s="3">
         <v>31100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>39100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>49000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>80900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>78600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>61900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>39400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>23400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>23200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,35 +4644,38 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4585,8 +4727,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4611,45 +4756,45 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>5900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>41500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>43100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>44400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>45200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>54000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>52300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>59000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>59200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>59300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>58300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,8 +4810,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,71 +5059,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E66" s="3">
         <v>31400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>56200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>85100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>84600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>82500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>78500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>80300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>77400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>75600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>71400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>70300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>69400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>68100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15700</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4985,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5235,11 +5402,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>136000</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,71 +5505,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-417800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-389100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-354700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-319900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-333100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-305100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-286200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-274300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-239300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-207700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-283100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-245000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-210300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-182000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-151100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-124800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-103400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-88100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-74300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-62500</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,71 +5837,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>151100</v>
+      </c>
+      <c r="E76" s="3">
         <v>175000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>203700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>232000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>212100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>233400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>245400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>251200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>279500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>305800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>225500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>258700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>288400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>218300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>245100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>267700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>286800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>300800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>313700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-58100</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5735,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>75500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-38100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-15300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-13800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6207,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6022,10 +6220,10 @@
         <v>500</v>
       </c>
       <c r="F83" s="3">
+        <v>500</v>
+      </c>
+      <c r="G83" s="3">
         <v>400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>500</v>
       </c>
       <c r="H83" s="3">
         <v>500</v>
@@ -6049,7 +6247,7 @@
         <v>500</v>
       </c>
       <c r="O83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
@@ -6058,13 +6256,13 @@
         <v>400</v>
       </c>
       <c r="R83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
       </c>
       <c r="T83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
@@ -6076,13 +6274,13 @@
         <v>200</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3">
+        <v>100</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
@@ -6090,8 +6288,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-30500</v>
+        <v>-27300</v>
       </c>
       <c r="E89" s="3">
         <v>-30500</v>
       </c>
       <c r="F89" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="G89" s="3">
         <v>11900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-34300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-31800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-29600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-20700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-14200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-20100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>36700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6819,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6614,74 +6834,77 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7066,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E94" s="3">
         <v>31100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-20300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>31900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>24500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>28400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>34100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-208900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>400</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-400</v>
       </c>
       <c r="P94" s="3">
         <v>-400</v>
       </c>
       <c r="Q94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6976,8 +7209,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7030,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,159 +7512,165 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
-      </c>
-      <c r="M100" s="3">
-        <v>200</v>
       </c>
       <c r="N100" s="3">
         <v>200</v>
       </c>
       <c r="O100" s="3">
+        <v>200</v>
+      </c>
+      <c r="P100" s="3">
         <v>94600</v>
-      </c>
-      <c r="P100" s="3">
-        <v>400</v>
       </c>
       <c r="Q100" s="3">
         <v>400</v>
       </c>
       <c r="R100" s="3">
+        <v>400</v>
+      </c>
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>249000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>21000</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
       <c r="S101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T101" s="3">
         <v>200</v>
       </c>
       <c r="U101" s="3">
+        <v>200</v>
+      </c>
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
@@ -7430,84 +7678,90 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-120600</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-29300</v>
       </c>
       <c r="N102" s="3">
         <v>-29300</v>
       </c>
       <c r="O102" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="P102" s="3">
         <v>73400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-14800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-22100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>286200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>23700</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>RPTX</t>
   </si>
@@ -656,185 +656,189 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>1100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>52400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>112500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6900</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>300</v>
       </c>
       <c r="R8" s="3">
         <v>300</v>
       </c>
       <c r="S8" s="3">
+        <v>300</v>
+      </c>
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -850,8 +854,8 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
@@ -859,38 +863,41 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
         <v>-78100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>28400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>33000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>-85100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>32700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>33800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -942,38 +949,41 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>78100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-28400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-29000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>98100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-30600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-3500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-26200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1025,8 +1035,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E12" s="3">
         <v>100000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>28600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>33300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>118000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>34200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>31500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3700</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,20 +1239,23 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1251,14 +1271,14 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1275,18 +1295,18 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1299,19 +1319,22 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
         <v>500</v>
@@ -1332,11 +1355,11 @@
         <v>500</v>
       </c>
       <c r="K15" s="3">
+        <v>500</v>
+      </c>
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1373,8 +1396,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
@@ -1388,8 +1411,11 @@
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,148 +1442,152 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E17" s="3">
         <v>30800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>43900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>35200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4800</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-34800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-38400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-34700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>73400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-38700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-34800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-31700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-26600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,8 +1612,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,8 +1646,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1622,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
@@ -1643,35 +1677,35 @@
         <v>100</v>
       </c>
       <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1696,65 +1730,68 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-30400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-34400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-36900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-30400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-38000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-34300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>76000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-37500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-34200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-31200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-26300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-21200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1779,8 +1816,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1808,8 +1848,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1862,147 +1902,153 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-28700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-33900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-34400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>75500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-38100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-34700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-26700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-21600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-12500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-16300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1600</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>100</v>
@@ -2011,25 +2057,28 @@
         <v>100</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-18900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>75500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-38100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-15300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-18900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>75500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-38100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-21400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-15300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-13800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,8 +2676,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2618,16 +2688,16 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
@@ -2639,35 +2709,35 @@
         <v>-100</v>
       </c>
       <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,91 +2762,97 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-18900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>75500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-38100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-21400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-15300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-13800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-18900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>75500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-38100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-21400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-15300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-13800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,74 +3177,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E41" s="3">
         <v>84700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>80500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>79800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>103200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>111300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>107400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>115500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>121500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>159500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>155200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>275800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>305100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>334400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>261000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>293600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>311400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>326200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>347900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>369900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>83700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,58 +3261,61 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E42" s="3">
         <v>68100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>98900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>128300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>133800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>112400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>142700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>165100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>192700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>184400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>215200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7400</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>7200</v>
       </c>
       <c r="R42" s="3">
         <v>7200</v>
       </c>
       <c r="S42" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3257,74 +3347,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E43" s="3">
         <v>12300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19500</v>
-      </c>
-      <c r="J43" s="3">
-        <v>7000</v>
       </c>
       <c r="K43" s="3">
         <v>7000</v>
       </c>
       <c r="L43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M43" s="3">
         <v>4300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,8 +3433,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3369,8 +3465,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3423,8 +3519,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3452,45 +3551,45 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>5700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>800</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,74 +3605,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>140300</v>
+      </c>
+      <c r="E46" s="3">
         <v>171100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>200400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>228500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>254700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>243700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>275100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>291900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>325500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>354000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>390600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>289700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>319200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>351400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>280400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>309200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>328200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>346600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>361300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>377300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>87900</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,8 +3691,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3630,8 +3735,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3672,74 +3777,77 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3100</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3755,8 +3863,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3838,8 +3949,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,74 +4121,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2700</v>
       </c>
       <c r="I52" s="3">
         <v>2700</v>
       </c>
       <c r="J52" s="3">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="K52" s="3">
         <v>400</v>
       </c>
       <c r="L52" s="3">
+        <v>400</v>
+      </c>
+      <c r="M52" s="3">
         <v>500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2600</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4087,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,74 +4293,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E54" s="3">
         <v>176500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>206400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>235300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>263100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>253900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>286400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>301600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>336300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>364100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>409200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>308000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>337100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>368700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>295600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>320700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>339100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>357100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>370200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>381700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>93600</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,74 +4445,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3300</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4398,28 +4529,31 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2300</v>
       </c>
       <c r="J58" s="3">
         <v>2300</v>
@@ -4428,7 +4562,7 @@
         <v>2300</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4481,74 +4615,77 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>57800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>78200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>52500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>34400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>32800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4000</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4564,74 +4701,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E60" s="3">
         <v>25300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>39100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>49000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>53300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>80900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>78600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>61900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>39400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>35100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>23400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7300</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4647,38 +4787,41 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4730,8 +4873,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4759,45 +4905,45 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>5900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>41500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>43100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>45200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>54000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>52300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>59000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>59200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>59300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>58300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4813,8 +4959,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,74 +5217,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E66" s="3">
         <v>25400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>56200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>85100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>84600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>82500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>78500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>80300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>77400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>75600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>71400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>70300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>69400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>68100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15700</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5145,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5405,11 +5573,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>136000</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,74 +5679,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-447800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-417800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-389100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-354700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-319900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-333100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-305100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-286200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-274300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-239300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-207700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-283100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-245000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-210300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-182000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-151100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-124800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-103400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-88100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-74300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-62500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5591,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,74 +6023,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E76" s="3">
         <v>151100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>175000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>203700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>232000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>212100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>233400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>245400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>251200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>279500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>305800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>225500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>258700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>288400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>218300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>245100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>267700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>286800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>300800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>313700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-58100</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5923,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-18900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>75500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-38100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-21400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-15300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-13800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,8 +6406,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6223,10 +6422,10 @@
         <v>500</v>
       </c>
       <c r="G83" s="3">
+        <v>500</v>
+      </c>
+      <c r="H83" s="3">
         <v>400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
@@ -6250,7 +6449,7 @@
         <v>500</v>
       </c>
       <c r="P83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q83" s="3">
         <v>400</v>
@@ -6259,13 +6458,13 @@
         <v>400</v>
       </c>
       <c r="S83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
@@ -6277,13 +6476,13 @@
         <v>200</v>
       </c>
       <c r="Y83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="AA83" s="3">
+        <v>100</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
@@ -6291,8 +6490,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27300</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-30500</v>
       </c>
       <c r="F89" s="3">
         <v>-30500</v>
       </c>
       <c r="G89" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="H89" s="3">
         <v>11900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-32900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-34300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-31800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-29600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>88200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-32800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-14200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-12900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-20100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>36700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,8 +7040,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6837,74 +7058,77 @@
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,91 +7296,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E94" s="3">
         <v>31600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>31100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>31900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>24500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>28400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>34100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-208900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>400</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-400</v>
       </c>
       <c r="Q94" s="3">
         <v>-400</v>
       </c>
       <c r="R94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7212,8 +7446,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,165 +7758,171 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
-      </c>
-      <c r="N100" s="3">
-        <v>200</v>
       </c>
       <c r="O100" s="3">
         <v>200</v>
       </c>
       <c r="P100" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q100" s="3">
         <v>94600</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>400</v>
       </c>
       <c r="R100" s="3">
         <v>400</v>
       </c>
       <c r="S100" s="3">
+        <v>400</v>
+      </c>
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>249000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>21000</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U101" s="3">
         <v>200</v>
       </c>
       <c r="V101" s="3">
+        <v>200</v>
+      </c>
+      <c r="W101" s="3">
         <v>500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>500</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
+      <c r="AA101" s="3">
+        <v>0</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
@@ -7681,87 +7930,93 @@
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-120600</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-29300</v>
       </c>
       <c r="O102" s="3">
         <v>-29300</v>
       </c>
       <c r="P102" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="Q102" s="3">
         <v>73400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-32900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-14800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-21700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-22100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>286200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>23700</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RPTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
   <si>
     <t>RPTX</t>
   </si>
@@ -656,192 +656,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>1100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>52400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>112500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6900</v>
-      </c>
-      <c r="R8" s="3">
-        <v>300</v>
       </c>
       <c r="S8" s="3">
         <v>300</v>
       </c>
       <c r="T8" s="3">
+        <v>300</v>
+      </c>
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,8 +861,8 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
@@ -866,41 +870,44 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>14300</v>
       </c>
       <c r="E9" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F9" s="3">
         <v>-78100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>28400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>33000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>-85100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>32700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -952,41 +959,44 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-14000</v>
       </c>
       <c r="E10" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="F10" s="3">
         <v>78100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-28400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-29000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>98100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-30600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-3500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-26200</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>20300</v>
+        <v>14400</v>
       </c>
       <c r="E12" s="3">
+        <v>20400</v>
+      </c>
+      <c r="F12" s="3">
         <v>100000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>28600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>118000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>34200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>31200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>31500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3700</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,23 +1259,26 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E14" s="3">
         <v>3300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1274,14 +1294,14 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1298,18 +1318,18 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-300</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1322,22 +1342,25 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>500</v>
       </c>
       <c r="F15" s="3">
         <v>500</v>
@@ -1358,11 +1381,11 @@
         <v>500</v>
       </c>
       <c r="L15" s="3">
+        <v>500</v>
+      </c>
+      <c r="M15" s="3">
         <v>400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1399,8 +1422,8 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>3</v>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,154 +1469,158 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E17" s="3">
         <v>27900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>30800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>40400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4800</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-27900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-30800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-34800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-37300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-30900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-38400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-34700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>73400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-38700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-28700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-31700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-26600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1615,8 +1645,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1659,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
@@ -1680,35 +1714,35 @@
         <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1733,68 +1767,71 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-26800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-30400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-34400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-36900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-30400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-38000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-34300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>76000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-37500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-28300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-31200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-26300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-21200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-16500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1819,8 +1856,11 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1851,8 +1891,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1905,153 +1945,159 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-29700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-34400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>75500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-38100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-28700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-31600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-26700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-21600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-16300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1600</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>100</v>
@@ -2060,25 +2106,28 @@
         <v>100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>75500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-38100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-28300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-26300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-21400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-15300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>75500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-38100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-28300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-30900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-26300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-21400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-15300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2691,16 +2761,16 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
@@ -2712,35 +2782,35 @@
         <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,94 +2835,100 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-30000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>75500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-38100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-28300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-30900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-26300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-21400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-15300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-30000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>75500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-38100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-28300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-30900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-26300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-21400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-15300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E41" s="3">
         <v>84500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>84700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>80500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>79800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>103200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>111300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>107400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>115500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>121500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>159500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>155200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>275800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>305100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>334400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>261000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>293600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>311400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>326200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>347900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>369900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>83700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,61 +3351,64 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E42" s="3">
         <v>39800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>68100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>98900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>128300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>133800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>112400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>142700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>165100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>192700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>184400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>215200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7400</v>
-      </c>
-      <c r="R42" s="3">
-        <v>7200</v>
       </c>
       <c r="S42" s="3">
         <v>7200</v>
       </c>
       <c r="T42" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3350,77 +3440,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E43" s="3">
         <v>11600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19500</v>
-      </c>
-      <c r="K43" s="3">
-        <v>7000</v>
       </c>
       <c r="L43" s="3">
         <v>7000</v>
       </c>
       <c r="M43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N43" s="3">
         <v>4300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3400</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3468,8 +3564,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3522,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3554,45 +3653,45 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>5700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>800</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,77 +3707,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E46" s="3">
         <v>140300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>171100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>228500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>254700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>243700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>275100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>291900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>325500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>354000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>390600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>289700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>319200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>351400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>280400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>309200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>328200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>346600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>361300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>377300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>87900</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,13 +3796,16 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>1600</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -3738,8 +3843,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3780,77 +3885,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3974,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,77 +4241,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2700</v>
       </c>
       <c r="J52" s="3">
         <v>2700</v>
       </c>
       <c r="K52" s="3">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
       </c>
       <c r="M52" s="3">
+        <v>400</v>
+      </c>
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>130500</v>
+      </c>
+      <c r="E54" s="3">
         <v>144000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>176500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>206400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>235300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>263100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>253900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>286400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>301600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>336300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>364100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>409200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>308000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>337100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>368700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>295600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>320700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>339100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>357100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>370200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>381700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>93600</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3300</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,31 +4663,34 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2300</v>
       </c>
       <c r="K58" s="3">
         <v>2300</v>
@@ -4565,7 +4699,7 @@
         <v>2300</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4618,77 +4752,80 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>3600</v>
       </c>
       <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>57800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>78200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>52500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>32500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>32800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,77 +4841,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E60" s="3">
         <v>18900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>39100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>49000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>80900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>78600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>61900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>34100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>35100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4930,11 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4799,32 +4942,32 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4876,8 +5019,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4908,45 +5054,45 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>5900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>41500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>43100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>44400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>45200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>54000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>52300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>59000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>59200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>59300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>58300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E66" s="3">
         <v>18900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>56200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>85100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>84600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>82500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>78500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>80300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>77400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>75600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>71400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>70300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>69400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>68100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15700</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5576,11 +5744,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>136000</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-464600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-447800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-417800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-389100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-354700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-319900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-333100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-305100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-286200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-274300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-239300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-207700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-283100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-245000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-210300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-182000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-151100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-124800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-103400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-88100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-74300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-62500</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E76" s="3">
         <v>125100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>151100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>175000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>203700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>232000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>212100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>233400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>245400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>251200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>279500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>305800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>225500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>258700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>288400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>218300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>245100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>267700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>286800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>300800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>313700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-58100</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-30000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>75500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-38100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-28300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-30900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-26300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-21400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-15300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6425,10 +6624,10 @@
         <v>500</v>
       </c>
       <c r="H83" s="3">
+        <v>500</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
@@ -6452,7 +6651,7 @@
         <v>500</v>
       </c>
       <c r="Q83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R83" s="3">
         <v>400</v>
@@ -6461,13 +6660,13 @@
         <v>400</v>
       </c>
       <c r="T83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U83" s="3">
         <v>300</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -6479,13 +6678,13 @@
         <v>200</v>
       </c>
       <c r="Z83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+      <c r="AB83" s="3">
+        <v>100</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-29100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27300</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-30500</v>
       </c>
       <c r="G89" s="3">
         <v>-30500</v>
       </c>
       <c r="H89" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="I89" s="3">
         <v>11900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-32900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-34300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-31800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-29600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>88200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-20700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-32800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-14200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-12900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-20100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>36700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7061,74 +7282,77 @@
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
         <v>28800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>31600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>31100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>7100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>31900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>24500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>28400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>34100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-208900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>400</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-400</v>
       </c>
       <c r="R94" s="3">
         <v>-400</v>
       </c>
       <c r="S94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7449,8 +7683,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,94 +8004,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
-      </c>
-      <c r="O100" s="3">
-        <v>200</v>
       </c>
       <c r="P100" s="3">
         <v>200</v>
       </c>
       <c r="Q100" s="3">
+        <v>200</v>
+      </c>
+      <c r="R100" s="3">
         <v>94600</v>
-      </c>
-      <c r="R100" s="3">
-        <v>400</v>
       </c>
       <c r="S100" s="3">
         <v>400</v>
       </c>
       <c r="T100" s="3">
+        <v>400</v>
+      </c>
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>249000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>21000</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7856,76 +8105,76 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V101" s="3">
         <v>200</v>
       </c>
       <c r="W101" s="3">
+        <v>200</v>
+      </c>
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>500</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3" t="s">
-        <v>3</v>
+      <c r="AB101" s="3">
+        <v>0</v>
       </c>
       <c r="AC101" s="3" t="s">
         <v>3</v>
@@ -7933,90 +8182,96 @@
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-120600</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-29300</v>
       </c>
       <c r="P102" s="3">
         <v>-29300</v>
       </c>
       <c r="Q102" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="R102" s="3">
         <v>73400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-32900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-21700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-22100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>286200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>23700</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
